--- a/data/fmsForecastOutput/File1/RPT_RPT6764446272771DP_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6764446272771DP_fmsForecastOutput.xlsx
@@ -1875,43 +1875,43 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>428.1491961764176</v>
+        <v>428.1491961764175</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>457.6440469708219</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>488.8331072009524</v>
+        <v>488.8331072009526</v>
       </c>
       <c r="F8" s="149" t="n">
         <v>548.3251848004671</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>579.8981852741937</v>
+        <v>579.8981852741938</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>428.1491961764176</v>
+        <v>428.1491961764175</v>
       </c>
       <c r="I8" s="149" t="n">
         <v>457.6440469708219</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>488.8331072009524</v>
+        <v>488.8331072009526</v>
       </c>
       <c r="K8" s="149" t="n">
         <v>548.3251848004671</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>579.8981852741937</v>
+        <v>579.8981852741938</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>5922418.392280672</v>
+        <v>5922418.392280671</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>6988943.336619967</v>
+        <v>6988943.336619969</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>8150469.052954222</v>
+        <v>8150469.052954224</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>9356437.141383851</v>
@@ -1925,43 +1925,43 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>427.054525622994</v>
+        <v>427.0545256229939</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>456.4739654510094</v>
+        <v>456.4739654510095</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>487.5832830443961</v>
+        <v>487.5832830443962</v>
       </c>
       <c r="W8" s="149" t="n">
         <v>546.9232542611551</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>578.4155304588336</v>
+        <v>578.4155304588337</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>427.054525622994</v>
+        <v>427.0545256229939</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>456.4739654510094</v>
+        <v>456.4739654510095</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>487.5832830443961</v>
+        <v>487.5832830443962</v>
       </c>
       <c r="AB8" s="149" t="n">
         <v>546.9232542611551</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>578.4155304588336</v>
+        <v>578.4155304588337</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>5922418.392280672</v>
+        <v>5922418.392280671</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>6988943.336619967</v>
+        <v>6988943.336619969</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>8150469.052954222</v>
+        <v>8150469.052954224</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>9356437.141383851</v>
@@ -2022,49 +2022,49 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>822.4012004297338</v>
+        <v>833.7244697813009</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>899.7593091805661</v>
+        <v>910.4986582981268</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>969.6772864589116</v>
+        <v>979.8352956975715</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>1228.767975189198</v>
+        <v>1240.309599904299</v>
       </c>
       <c r="G9" s="157" t="n">
-        <v>1306.622529855716</v>
+        <v>1316.691010341154</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>822.4012004297338</v>
+        <v>833.7244697813009</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>899.7593091805661</v>
+        <v>910.4986582981268</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>969.6772864589116</v>
+        <v>979.8352956975715</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>1228.767975189198</v>
+        <v>1240.309599904299</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>1306.622529855716</v>
+        <v>1316.691010341154</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>2341462.543834868</v>
+        <v>2373701.080265254</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>2751634.454676052</v>
+        <v>2784477.419179067</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>3192490.559190225</v>
+        <v>3225934.00377478</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>3566629.394625555</v>
+        <v>3600130.184686652</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>4168705.246906492</v>
+        <v>4200828.164175231</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,49 +2072,49 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>1016.559252236937</v>
+        <v>1030.55579579608</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>1112.180587839461</v>
+        <v>1125.455355316398</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>1198.60527528259</v>
+        <v>1211.161456220157</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1518.863850610043</v>
+        <v>1533.130300347533</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1615.098836446249</v>
+        <v>1627.544352075472</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>1016.559252236937</v>
+        <v>1030.55579579608</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>1112.180587839461</v>
+        <v>1125.455355316398</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>1198.60527528259</v>
+        <v>1211.161456220157</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>1518.863850610043</v>
+        <v>1533.130300347533</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1615.098836446249</v>
+        <v>1627.544352075472</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>2341462.543834868</v>
+        <v>2373701.080265254</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>2751634.454676052</v>
+        <v>2784477.419179067</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>3192490.559190225</v>
+        <v>3225934.00377478</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>3566629.394625555</v>
+        <v>3600130.184686652</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>4168705.246906492</v>
+        <v>4200828.164175231</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>495.4451439168041</v>
+        <v>497.3779435838002</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>531.4078193349045</v>
+        <v>533.1996029971259</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>568.1240433651639</v>
+        <v>569.7990934059923</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>647.2448776297281</v>
+        <v>648.9227467874217</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>685.7939340717669</v>
+        <v>687.2610780971586</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>495.4451439168041</v>
+        <v>497.3779435838002</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>531.4078193349045</v>
+        <v>533.1996029971259</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>568.1240433651639</v>
+        <v>569.7990934059923</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>647.2448776297281</v>
+        <v>648.9227467874217</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>685.7939340717669</v>
+        <v>687.2610780971586</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>8263880.93611554</v>
+        <v>8296119.472545925</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>9740577.79129602</v>
+        <v>9773420.755799035</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>11342959.61214445</v>
+        <v>11376403.056729</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>12923066.53600941</v>
+        <v>12956567.3260705</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>15015364.15398073</v>
+        <v>15047487.07124947</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>511.0188222660362</v>
+        <v>513.0123769948123</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>547.6909834085044</v>
+        <v>549.5376701156092</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>585.3053323066811</v>
+        <v>587.0310394514976</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>664.2328803231638</v>
+        <v>665.954787907047</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>703.8414029544053</v>
+        <v>705.3471565895195</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>511.0188222660362</v>
+        <v>513.0123769948123</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>547.6909834085044</v>
+        <v>549.5376701156092</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>585.3053323066811</v>
+        <v>587.0310394514976</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>664.2328803231638</v>
+        <v>665.954787907047</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>703.8414029544053</v>
+        <v>705.3471565895195</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>8263880.93611554</v>
+        <v>8296119.472545925</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>9740577.79129602</v>
+        <v>9773420.755799035</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>11342959.61214445</v>
+        <v>11376403.056729</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>12923066.53600941</v>
+        <v>12956567.3260705</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>15015364.15398073</v>
+        <v>15047487.07124947</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>1229.169584201536</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1308.046275033991</v>
+        <v>1308.046275033992</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1411.101304321292</v>
@@ -2339,7 +2339,7 @@
         <v>1229.169584201536</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>1308.046275033991</v>
+        <v>1308.046275033992</v>
       </c>
       <c r="K11" s="156" t="n">
         <v>1411.101304321292</v>
@@ -2360,7 +2360,7 @@
         <v>153087.2164553095</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>185294.9783859461</v>
+        <v>185294.9783859462</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>1261.548820008225</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1342.503309547174</v>
+        <v>1342.503309547175</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1448.273052196445</v>
@@ -2389,7 +2389,7 @@
         <v>1261.548820008225</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>1342.503309547174</v>
+        <v>1342.503309547175</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>1448.273052196445</v>
@@ -2410,7 +2410,7 @@
         <v>153087.2164553095</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>185294.9783859461</v>
+        <v>185294.9783859462</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,49 +2461,49 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>498.4245987430613</v>
+        <v>500.3482611214206</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>534.7108252907444</v>
+        <v>536.4941271581673</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>571.7558769619732</v>
+        <v>573.4227051887322</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>651.372900913608</v>
+        <v>653.0417025519247</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>690.3336022407429</v>
+        <v>691.7924553733279</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>498.4245987430613</v>
+        <v>500.3482611214206</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>534.7108252907444</v>
+        <v>536.4941271581673</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>571.7558769619732</v>
+        <v>573.4227051887322</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>651.372900913608</v>
+        <v>653.0417025519247</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>690.3336022407429</v>
+        <v>691.7924553733279</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>8353066.40351511</v>
+        <v>8385304.939945497</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>9847737.48921214</v>
+        <v>9880580.453715157</v>
       </c>
       <c r="O12" s="165" t="n">
-        <v>11471779.56318452</v>
+        <v>11505223.00776908</v>
       </c>
       <c r="P12" s="165" t="n">
-        <v>13076153.75246472</v>
+        <v>13109654.54252581</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>15200659.13236668</v>
+        <v>15232782.04963542</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2511,49 +2511,49 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>514.0798764660177</v>
+        <v>516.0639601575593</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>551.0842712668709</v>
+        <v>552.9221798402074</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>589.0360145988719</v>
+        <v>590.7532192578393</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>668.4695872874313</v>
+        <v>670.1821902232696</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>708.5006399949432</v>
+        <v>709.9978847686876</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>514.0798764660177</v>
+        <v>516.0639601575593</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>551.0842712668709</v>
+        <v>552.9221798402074</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>589.0360145988719</v>
+        <v>590.7532192578393</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>668.4695872874313</v>
+        <v>670.1821902232696</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>708.5006399949432</v>
+        <v>709.9978847686876</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>8353066.40351511</v>
+        <v>8385304.939945497</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>9847737.48921214</v>
+        <v>9880580.453715157</v>
       </c>
       <c r="AF12" s="165" t="n">
-        <v>11471779.56318452</v>
+        <v>11505223.00776908</v>
       </c>
       <c r="AG12" s="165" t="n">
-        <v>13076153.75246472</v>
+        <v>13109654.54252581</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>15200659.13236668</v>
+        <v>15232782.04963542</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>2376.864647831991</v>
+        <v>2376.89260476876</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>2447.055425541019</v>
+        <v>2447.078998650416</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>2560.780796691275</v>
+        <v>2560.801397512608</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>2674.755393938892</v>
+        <v>2674.773089479312</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>2824.36252760349</v>
+        <v>2824.377798604442</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>2376.864647831991</v>
+        <v>2376.89260476876</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>2447.055425541019</v>
+        <v>2447.078998650416</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>2560.780796691275</v>
+        <v>2560.801397512608</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>2674.755393938892</v>
+        <v>2674.773089479312</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>2824.36252760349</v>
+        <v>2824.377798604442</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>3033348.543912366</v>
+        <v>3033384.222483091</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>3547444.608490058</v>
+        <v>3547478.781929271</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>4176084.256694561</v>
+        <v>4176117.8522158</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>4922193.377377147</v>
+        <v>4922225.941428448</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>5900654.031609965</v>
+        <v>5900685.935762656</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2653,49 +2653,49 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>1263.999616774518</v>
+        <v>1264.014484073501</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>1301.326570249232</v>
+        <v>1301.339106260178</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>1361.804909090521</v>
+        <v>1361.815864459937</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>1422.415784587542</v>
+        <v>1422.425194949353</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>1501.975788053147</v>
+        <v>1501.983909062212</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>1263.999616774518</v>
+        <v>1264.014484073501</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>1301.326570249232</v>
+        <v>1301.339106260178</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>1361.804909090521</v>
+        <v>1361.815864459937</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>1422.415784587542</v>
+        <v>1422.425194949353</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>1501.975788053147</v>
+        <v>1501.983909062212</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>3033348.543912366</v>
+        <v>3033384.222483091</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>3547444.608490058</v>
+        <v>3547478.781929271</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>4176084.256694561</v>
+        <v>4176117.8522158</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>4922193.377377147</v>
+        <v>4922225.941428448</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>5900654.031609965</v>
+        <v>5900685.935762656</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,49 +2746,49 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>631.3462787277081</v>
+        <v>633.1357976969259</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>674.2557345162295</v>
+        <v>675.9106279421155</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>721.2689860906605</v>
+        <v>722.8120689710055</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>821.2798451047668</v>
+        <v>822.8100004947365</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>875.26469757107</v>
+        <v>876.5984524814005</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>631.3462787277081</v>
+        <v>633.1357976969259</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>674.2557345162295</v>
+        <v>675.9106279421155</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>721.2689860906605</v>
+        <v>722.8120689710055</v>
       </c>
       <c r="K14" s="168" t="n">
-        <v>821.2798451047668</v>
+        <v>822.8100004947365</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>875.26469757107</v>
+        <v>876.5984524814005</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>11386414.94742748</v>
+        <v>11418689.16242859</v>
       </c>
       <c r="N14" s="171" t="n">
-        <v>13395182.0977022</v>
+        <v>13428059.23564443</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>15647863.81987908</v>
+        <v>15681340.85998488</v>
       </c>
       <c r="P14" s="171" t="n">
-        <v>17998347.12984186</v>
+        <v>18031880.48395426</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>21101313.16397664</v>
+        <v>21133467.98539807</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,49 +2796,49 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>610.5847129434358</v>
+        <v>612.315384308647</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>650.3850892668173</v>
+        <v>651.981394575654</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>694.1619109050505</v>
+        <v>695.6470009083108</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>781.7966538727893</v>
+        <v>783.253246739294</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>831.3075456187444</v>
+        <v>832.5743172868362</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>610.5847129434358</v>
+        <v>612.315384308647</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>650.3850892668173</v>
+        <v>651.981394575654</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>694.1619109050505</v>
+        <v>695.6470009083108</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>781.7966538727893</v>
+        <v>783.253246739294</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>831.3075456187444</v>
+        <v>832.5743172868362</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>11386414.94742748</v>
+        <v>11418689.16242859</v>
       </c>
       <c r="AE14" s="171" t="n">
-        <v>13395182.0977022</v>
+        <v>13428059.23564443</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>15647863.81987908</v>
+        <v>15681340.85998488</v>
       </c>
       <c r="AG14" s="171" t="n">
-        <v>17998347.12984186</v>
+        <v>18031880.48395426</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>21101313.16397664</v>
+        <v>21133467.98539807</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -4408,43 +4408,43 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>438.2677603877489</v>
+        <v>438.2677603877488</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>479.2500286209769</v>
+        <v>479.250028620977</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>515.0430396225207</v>
+        <v>515.0430396225208</v>
       </c>
       <c r="F35" s="149" t="n">
         <v>587.2974534163963</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>622.8117376486604</v>
+        <v>622.8117376486605</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>438.2677603877489</v>
+        <v>438.2677603877488</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>479.2500286209769</v>
+        <v>479.250028620977</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>515.0430396225207</v>
+        <v>515.0430396225208</v>
       </c>
       <c r="K35" s="149" t="n">
         <v>587.2974534163963</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>622.8117376486604</v>
+        <v>622.8117376486605</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>6062384.486632437</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>7318900.609055792</v>
+        <v>7318900.609055794</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>8587475.548494624</v>
+        <v>8587475.548494626</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>10021446.86858571</v>
@@ -4458,43 +4458,43 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>437.1472191930068</v>
+        <v>437.1472191930067</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>478.0247060027309</v>
+        <v>478.024706002731</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>513.7262032153626</v>
+        <v>513.7262032153627</v>
       </c>
       <c r="W35" s="149" t="n">
         <v>585.7958805205529</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>621.2193635986348</v>
+        <v>621.2193635986349</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>437.1472191930068</v>
+        <v>437.1472191930067</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>478.0247060027309</v>
+        <v>478.024706002731</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>513.7262032153626</v>
+        <v>513.7262032153627</v>
       </c>
       <c r="AB35" s="149" t="n">
         <v>585.7958805205529</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>621.2193635986348</v>
+        <v>621.2193635986349</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>6062384.486632437</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>7318900.609055792</v>
+        <v>7318900.609055794</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>8587475.548494624</v>
+        <v>8587475.548494626</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>10021446.86858571</v>
@@ -4510,49 +4510,49 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>836.4287367100035</v>
+        <v>848.2424265052475</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>934.6678262997061</v>
+        <v>946.1733500128992</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>1012.099986044415</v>
+        <v>1023.085205904455</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1316.190234817959</v>
+        <v>1328.638843946275</v>
       </c>
       <c r="G36" s="157" t="n">
-        <v>1403.116607786503</v>
+        <v>1414.005820488185</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>836.4287367100035</v>
+        <v>848.2424265052475</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>934.6678262997061</v>
+        <v>946.1733500128992</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>1012.099986044415</v>
+        <v>1023.085205904455</v>
       </c>
       <c r="K36" s="156" t="n">
-        <v>1316.190234817959</v>
+        <v>1328.638843946275</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1403.116607786503</v>
+        <v>1414.005820488185</v>
       </c>
       <c r="M36" s="158" t="n">
-        <v>2381400.412074084</v>
+        <v>2415035.226986312</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>2858391.314523553</v>
+        <v>2893577.386115463</v>
       </c>
       <c r="O36" s="159" t="n">
-        <v>3332159.776788035</v>
+        <v>3368326.665693805</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>3820381.776875355</v>
+        <v>3856515.18540793</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>4476564.142474362</v>
+        <v>4511305.559438291</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,49 +4560,49 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>1033.898504397983</v>
+        <v>1048.501250184512</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>1155.330544382314</v>
+        <v>1169.552370148578</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1251.043413439462</v>
+        <v>1264.622098490925</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>1626.92535007118</v>
+        <v>1642.312911252095</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1734.373890586926</v>
+        <v>1747.833902459095</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>1033.898504397983</v>
+        <v>1048.501250184512</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>1155.330544382314</v>
+        <v>1169.552370148578</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>1251.043413439462</v>
+        <v>1264.622098490925</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>1626.92535007118</v>
+        <v>1642.312911252095</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1734.373890586926</v>
+        <v>1747.833902459095</v>
       </c>
       <c r="AD36" s="158" t="n">
-        <v>2381400.412074084</v>
+        <v>2415035.226986312</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>2858391.314523553</v>
+        <v>2893577.386115463</v>
       </c>
       <c r="AF36" s="159" t="n">
-        <v>3332159.776788035</v>
+        <v>3368326.665693805</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>3820381.776875355</v>
+        <v>3856515.18540793</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>4476564.142474362</v>
+        <v>4511305.559438291</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>506.2309412106104</v>
+        <v>508.2474520780378</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>555.2332339747622</v>
+        <v>557.1528483935626</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>597.0074520222659</v>
+        <v>598.8189086317989</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>693.260586629281</v>
+        <v>695.0703090754855</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>736.5150546349963</v>
+        <v>738.1017929099123</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>506.2309412106104</v>
+        <v>508.2474520780378</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>555.2332339747622</v>
+        <v>557.1528483935626</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>597.0074520222659</v>
+        <v>598.8189086317989</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>693.260586629281</v>
+        <v>695.0703090754855</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>736.5150546349963</v>
+        <v>738.1017929099123</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>8443784.898706522</v>
+        <v>8477419.713618748</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>10177291.92357935</v>
+        <v>10212477.99517126</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>11919635.32528266</v>
+        <v>11955802.21418843</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>13841828.64546107</v>
+        <v>13877962.05399364</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>16125896.13409467</v>
+        <v>16160637.55105861</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>522.1436571704764</v>
+        <v>524.2235544531763</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>572.2464458978422</v>
+        <v>574.2248802952016</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>615.0622371580544</v>
+        <v>616.9284760986238</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>711.4563470284053</v>
+        <v>713.3135686064733</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>755.8973090845215</v>
+        <v>757.5258042316094</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>522.1436571704764</v>
+        <v>524.2235544531763</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>572.2464458978422</v>
+        <v>574.2248802952016</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>615.0622371580544</v>
+        <v>616.9284760986238</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>711.4563470284053</v>
+        <v>713.3135686064733</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>755.8973090845215</v>
+        <v>757.5258042316094</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>8443784.898706522</v>
+        <v>8477419.713618748</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>10177291.92357935</v>
+        <v>10212477.99517126</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>11919635.32528266</v>
+        <v>11955802.21418843</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>13841828.64546107</v>
+        <v>13877962.05399364</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>16125896.13409467</v>
+        <v>16160637.55105861</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4756,7 +4756,7 @@
         <v>163475.3638959133</v>
       </c>
       <c r="Q38" s="160" t="n">
-        <v>198363.4595920323</v>
+        <v>198363.4595920324</v>
       </c>
       <c r="S38" s="32" t="inlineStr">
         <is>
@@ -4770,13 +4770,13 @@
         <v>1320.217841417656</v>
       </c>
       <c r="V38" s="156" t="n">
-        <v>1413.255207802415</v>
+        <v>1413.255207802416</v>
       </c>
       <c r="W38" s="156" t="n">
         <v>1546.549540258803</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1636.145691308762</v>
+        <v>1636.145691308763</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>1181.675092922695</v>
@@ -4785,13 +4785,13 @@
         <v>1320.217841417656</v>
       </c>
       <c r="AA38" s="156" t="n">
-        <v>1413.255207802415</v>
+        <v>1413.255207802416</v>
       </c>
       <c r="AB38" s="156" t="n">
         <v>1546.549540258803</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1636.145691308762</v>
+        <v>1636.145691308763</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>91218.47196342691</v>
@@ -4806,7 +4806,7 @@
         <v>163475.3638959133</v>
       </c>
       <c r="AH38" s="160" t="n">
-        <v>198363.4595920323</v>
+        <v>198363.4595920324</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" thickTop="1">
@@ -4816,49 +4816,49 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>509.2807149846992</v>
+        <v>511.2876928197334</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>558.6940515693062</v>
+        <v>560.6045790788241</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>600.8358795342053</v>
+        <v>602.6384447917935</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>697.6574054914513</v>
+        <v>699.4573478583972</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>741.3615969604461</v>
+        <v>742.9393685104042</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>509.2807149846992</v>
+        <v>511.2876928197334</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>558.6940515693062</v>
+        <v>560.6045790788241</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>600.8358795342053</v>
+        <v>602.6384447917935</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>697.6574054914513</v>
+        <v>699.4573478583972</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>741.3615969604461</v>
+        <v>742.9393685104042</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>8535003.370669948</v>
+        <v>8568638.185582176</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>10289435.14215797</v>
+        <v>10324621.21374988</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>12055244.27714263</v>
+        <v>12091411.16604841</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>14005304.00935698</v>
+        <v>14041437.41788955</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>16324259.59368671</v>
+        <v>16359001.01065064</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4866,49 +4866,49 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>525.2769781148448</v>
+        <v>527.3469941616177</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>575.8018908683875</v>
+        <v>577.7709208758603</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>618.9949000425835</v>
+        <v>620.8519441031114</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>715.9689284936104</v>
+        <v>717.8161142292863</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>760.8715035878765</v>
+        <v>762.4907962737354</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>525.2769781148448</v>
+        <v>527.3469941616177</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>575.8018908683875</v>
+        <v>577.7709208758603</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>618.9949000425835</v>
+        <v>620.8519441031114</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>715.9689284936104</v>
+        <v>717.8161142292863</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>760.8715035878765</v>
+        <v>762.4907962737354</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>8535003.370669948</v>
+        <v>8568638.185582176</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>10289435.14215797</v>
+        <v>10324621.21374988</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>12055244.27714263</v>
+        <v>12091411.16604841</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>14005304.00935698</v>
+        <v>14041437.41788955</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>16324259.59368671</v>
+        <v>16359001.01065064</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>2427.219874847632</v>
+        <v>2427.248800364533</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>2552.908375242976</v>
+        <v>2552.933366835141</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>2683.221818563085</v>
+        <v>2683.243829177099</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>2831.56599482617</v>
+        <v>2831.585170167327</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>2990.463449232881</v>
+        <v>2990.480064664491</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>2427.219874847632</v>
+        <v>2427.248800364533</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>2552.908375242976</v>
+        <v>2552.933366835141</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>2683.221818563085</v>
+        <v>2683.243829177099</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>2831.56599482617</v>
+        <v>2831.585170167327</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>2990.463449232881</v>
+        <v>2990.480064664491</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>3097611.75498145</v>
+        <v>3097648.669651645</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>3700897.395784386</v>
+        <v>3700933.625568131</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>4375759.302865295</v>
+        <v>4375795.197456032</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>5210762.60615184</v>
+        <v>5210797.893392485</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>6247671.832365956</v>
+        <v>6247706.545301198</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>1290.778166284445</v>
+        <v>1290.793548667413</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>1357.618411679818</v>
+        <v>1357.631702029754</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>1426.918168637973</v>
+        <v>1426.929873725052</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>1505.806540392041</v>
+        <v>1505.816737701297</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1590.30706996983</v>
+        <v>1590.315905937501</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>1290.778166284445</v>
+        <v>1290.793548667413</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>1357.618411679818</v>
+        <v>1357.631702029754</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>1426.918168637973</v>
+        <v>1426.929873725052</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>1505.806540392041</v>
+        <v>1505.816737701297</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1590.30706996983</v>
+        <v>1590.315905937501</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>3097611.75498145</v>
+        <v>3097648.669651645</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>3700897.395784386</v>
+        <v>3700933.625568131</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>4375759.302865295</v>
+        <v>4375795.197456032</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>5210762.60615184</v>
+        <v>5210797.893392485</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>6247671.832365956</v>
+        <v>6247706.545301198</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,49 +5020,49 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>644.997420642125</v>
+        <v>646.8644280600297</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>704.2130426218522</v>
+        <v>705.9859814674892</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>757.3668475788097</v>
+        <v>759.0355702394079</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>876.8454180629321</v>
+        <v>878.4958263280899</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>936.2647044614412</v>
+        <v>937.7071890396453</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>644.997420642125</v>
+        <v>646.8644280600297</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>704.2130426218522</v>
+        <v>705.9859814674892</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>757.3668475788097</v>
+        <v>759.0355702394079</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>876.8454180629321</v>
+        <v>878.4958263280899</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>936.2647044614412</v>
+        <v>937.7071890396453</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>11632615.1256514</v>
+        <v>11666286.85523382</v>
       </c>
       <c r="N41" s="183" t="n">
-        <v>13990332.53794236</v>
+        <v>14025554.83931801</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>16431003.58000793</v>
+        <v>16467206.36350444</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>19216066.61550882</v>
+        <v>19252235.31128204</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>22571931.42605266</v>
+        <v>22606707.55595184</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,49 +5070,49 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>623.7869426040928</v>
+        <v>625.5925542418486</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>679.2818201495711</v>
+        <v>680.9919917215066</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>728.9031253388149</v>
+        <v>730.5091332681585</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>834.6909009045991</v>
+        <v>836.2619654654976</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>889.2440374611375</v>
+        <v>890.6140782243805</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>623.7869426040928</v>
+        <v>625.5925542418486</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>679.2818201495711</v>
+        <v>680.9919917215066</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>728.9031253388149</v>
+        <v>730.5091332681585</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>834.6909009045991</v>
+        <v>836.2619654654976</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>889.2440374611375</v>
+        <v>890.6140782243805</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>11632615.1256514</v>
+        <v>11666286.85523382</v>
       </c>
       <c r="AE41" s="189" t="n">
-        <v>13990332.53794236</v>
+        <v>14025554.83931801</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>16431003.58000793</v>
+        <v>16467206.36350444</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>19216066.61550882</v>
+        <v>19252235.31128204</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>22571931.42605266</v>
+        <v>22606707.55595184</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.299318825744664</v>
+        <v>0.2993188257446637</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.1875381125442845</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.1328816196537178</v>
+        <v>0.1328816196537179</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.09241680647937345</v>
+        <v>0.09241680647937361</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0.04991377355825401</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.299318825744664</v>
+        <v>0.2993188257446637</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.1875381125442845</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.1328816196537178</v>
+        <v>0.1328816196537179</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.09241680647937345</v>
+        <v>0.09241680647937361</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0.04991377355825401</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>4140.358862230863</v>
+        <v>4140.358862230861</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2864.001511008903</v>
+        <v>2864.001511008902</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>2215.57728545754</v>
+        <v>2215.577285457541</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>1576.969405383688</v>
+        <v>1576.969405383691</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>933.6081579481632</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.2985535422697581</v>
+        <v>0.2985535422697579</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.1870586244329434</v>
+        <v>0.1870586244329433</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.1325418745428424</v>
+        <v>0.1325418745428425</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.09218051978866404</v>
+        <v>0.09218051978866419</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0.04978615650650563</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.2985535422697581</v>
+        <v>0.2985535422697579</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.1870586244329434</v>
+        <v>0.1870586244329433</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.1325418745428424</v>
+        <v>0.1325418745428425</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.09218051978866404</v>
+        <v>0.09218051978866419</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0.04978615650650563</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>4140.358862230863</v>
+        <v>4140.358862230861</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2864.001511008903</v>
+        <v>2864.001511008902</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>2215.57728545754</v>
+        <v>2215.577285457541</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>1576.969405383688</v>
+        <v>1576.969405383691</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>933.6081579481632</v>
@@ -6436,49 +6436,49 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>0.3072446267357642</v>
+        <v>0.3028245146066884</v>
       </c>
       <c r="D58" s="156" t="n">
-        <v>0.1386758831475282</v>
+        <v>0.1368231872636654</v>
       </c>
       <c r="E58" s="156" t="n">
-        <v>0.1003246945066979</v>
+        <v>0.09906662286346044</v>
       </c>
       <c r="F58" s="156" t="n">
-        <v>0.08045488181807474</v>
+        <v>0.07947223107330424</v>
       </c>
       <c r="G58" s="157" t="n">
-        <v>0.04305651726597487</v>
+        <v>0.04260503889563629</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>0.3072446267357642</v>
+        <v>0.3028245146066884</v>
       </c>
       <c r="I58" s="156" t="n">
-        <v>0.1386758831475282</v>
+        <v>0.1368231872636654</v>
       </c>
       <c r="J58" s="156" t="n">
-        <v>0.1003246945066979</v>
+        <v>0.09906662286346044</v>
       </c>
       <c r="K58" s="156" t="n">
-        <v>0.08045488181807474</v>
+        <v>0.07947223107330424</v>
       </c>
       <c r="L58" s="157" t="n">
-        <v>0.04305651726597487</v>
+        <v>0.04260503889563629</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>874.7577033209631</v>
+        <v>862.1731801169924</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>424.0971270960099</v>
+        <v>418.4312320326777</v>
       </c>
       <c r="O58" s="159" t="n">
-        <v>330.3012708855981</v>
+        <v>326.1592930338865</v>
       </c>
       <c r="P58" s="159" t="n">
-        <v>233.5288290609032</v>
+        <v>230.6765810354698</v>
       </c>
       <c r="Q58" s="160" t="n">
-        <v>137.3693820050766</v>
+        <v>135.9289658111946</v>
       </c>
       <c r="S58" s="32" t="inlineStr">
         <is>
@@ -6486,49 +6486,49 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>0.3797810215319734</v>
+        <v>0.3743173793602586</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.1714154259527894</v>
+        <v>0.1691253330621931</v>
       </c>
       <c r="V58" s="156" t="n">
-        <v>0.1240100286518754</v>
+        <v>0.1224549429245665</v>
       </c>
       <c r="W58" s="156" t="n">
-        <v>0.0994492158535962</v>
+        <v>0.09823457425799542</v>
       </c>
       <c r="X58" s="157" t="n">
-        <v>0.05322159181304098</v>
+        <v>0.05266352536771877</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>0.3797810215319734</v>
+        <v>0.3743173793602586</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.1714154259527894</v>
+        <v>0.1691253330621931</v>
       </c>
       <c r="AA58" s="156" t="n">
-        <v>0.1240100286518754</v>
+        <v>0.1224549429245665</v>
       </c>
       <c r="AB58" s="156" t="n">
-        <v>0.0994492158535962</v>
+        <v>0.09823457425799542</v>
       </c>
       <c r="AC58" s="157" t="n">
-        <v>0.05322159181304098</v>
+        <v>0.05266352536771877</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>874.7577033209631</v>
+        <v>862.1731801169924</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>424.0971270960099</v>
+        <v>418.4312320326777</v>
       </c>
       <c r="AF58" s="159" t="n">
-        <v>330.3012708855981</v>
+        <v>326.1592930338865</v>
       </c>
       <c r="AG58" s="159" t="n">
-        <v>233.5288290609032</v>
+        <v>230.6765810354698</v>
       </c>
       <c r="AH58" s="160" t="n">
-        <v>137.3693820050766</v>
+        <v>135.9289658111946</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" thickTop="1">
@@ -6538,49 +6538,49 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.3006717022894718</v>
+        <v>0.2999172213188339</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1793857987146072</v>
+        <v>0.1790766896448273</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.1275130009100759</v>
+        <v>0.1273055455999007</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.09067783601799721</v>
+        <v>0.09053498270071021</v>
       </c>
       <c r="G59" s="163" t="n">
-        <v>0.04891455797509377</v>
+        <v>0.04884877011419523</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.3006717022894718</v>
+        <v>0.2999172213188339</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.1793857987146072</v>
+        <v>0.1790766896448273</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.1275130009100759</v>
+        <v>0.1273055455999007</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.09067783601799721</v>
+        <v>0.09053498270071021</v>
       </c>
       <c r="L59" s="163" t="n">
-        <v>0.04891455797509377</v>
+        <v>0.04884877011419523</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>5015.116565551826</v>
+        <v>5002.532042347853</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="Q59" s="166" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
       <c r="S59" s="42" t="inlineStr">
         <is>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.3101229290048125</v>
+        <v>0.3093447318990956</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.1848824592579155</v>
+        <v>0.1845638786043224</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.1313692674033209</v>
+        <v>0.1311555381998504</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.09305782445166373</v>
+        <v>0.09291122171491786</v>
       </c>
       <c r="X59" s="163" t="n">
-        <v>0.05020180173609083</v>
+        <v>0.05013428259074455</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.3101229290048125</v>
+        <v>0.3093447318990956</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.1848824592579155</v>
+        <v>0.1845638786043224</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.1313692674033209</v>
+        <v>0.1311555381998504</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.09305782445166373</v>
+        <v>0.09291122171491786</v>
       </c>
       <c r="AC59" s="163" t="n">
-        <v>0.05020180173609083</v>
+        <v>0.05013428259074455</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>5015.116565551826</v>
+        <v>5002.532042347853</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="AH59" s="166" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" thickBot="1">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="C60" s="155" t="n">
-        <v>0.3794310678768666</v>
+        <v>0.3794310678768665</v>
       </c>
       <c r="D60" s="156" t="n">
         <v>0</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="155" t="n">
-        <v>0.3794310678768666</v>
+        <v>0.3794310678768665</v>
       </c>
       <c r="I60" s="156" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="158" t="n">
-        <v>30.06144524010886</v>
+        <v>30.06144524010885</v>
       </c>
       <c r="N60" s="159" t="n">
         <v>0</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="T60" s="155" t="n">
-        <v>0.3894261801681862</v>
+        <v>0.3894261801681861</v>
       </c>
       <c r="U60" s="156" t="n">
         <v>0</v>
@@ -6705,7 +6705,7 @@
         <v>0</v>
       </c>
       <c r="Y60" s="155" t="n">
-        <v>0.3894261801681862</v>
+        <v>0.3894261801681861</v>
       </c>
       <c r="Z60" s="156" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="AD60" s="158" t="n">
-        <v>30.06144524010886</v>
+        <v>30.06144524010885</v>
       </c>
       <c r="AE60" s="159" t="n">
         <v>0</v>
@@ -6742,49 +6742,49 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.3010440363024151</v>
+        <v>0.3002931221320604</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.1785366373082628</v>
+        <v>0.1782289914729992</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.1268871162144767</v>
+        <v>0.1266806791777538</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.09018779599825763</v>
+        <v>0.09004571468706933</v>
       </c>
       <c r="G61" s="163" t="n">
-        <v>0.04863813974359796</v>
+        <v>0.04857272365267786</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.3010440363024151</v>
+        <v>0.3002931221320604</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.1785366373082628</v>
+        <v>0.1782289914729992</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.1268871162144767</v>
+        <v>0.1266806791777538</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.09018779599825763</v>
+        <v>0.09004571468706933</v>
       </c>
       <c r="L61" s="163" t="n">
-        <v>0.04863813974359796</v>
+        <v>0.04857272365267786</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>5045.178010791935</v>
+        <v>5032.593487587962</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="Q61" s="166" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
       <c r="S61" s="42" t="inlineStr">
         <is>
@@ -6792,49 +6792,49 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.3104996851749612</v>
+        <v>0.309725185150472</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.1840036296477888</v>
+        <v>0.1836865633515485</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.1307220165992105</v>
+        <v>0.1305093404304531</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.09255496918087837</v>
+        <v>0.0924091586393006</v>
       </c>
       <c r="X61" s="163" t="n">
-        <v>0.04991811643624035</v>
+        <v>0.04985097883474968</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.3104996851749612</v>
+        <v>0.309725185150472</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.1840036296477888</v>
+        <v>0.1836865633515485</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.1307220165992105</v>
+        <v>0.1305093404304531</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.09255496918087837</v>
+        <v>0.0924091586393006</v>
       </c>
       <c r="AC61" s="163" t="n">
-        <v>0.04991811643624035</v>
+        <v>0.04985097883474968</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>5045.178010791935</v>
+        <v>5032.593487587962</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="AH61" s="166" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" thickBot="1">
@@ -6946,49 +6946,49 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.2797416374986396</v>
+        <v>0.2790438593190216</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.1655087139709394</v>
+        <v>0.165223517233056</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.1173491325193396</v>
+        <v>0.1171582131580835</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.08261457003914181</v>
+        <v>0.08248441954256415</v>
       </c>
       <c r="G63" s="181" t="n">
-        <v>0.04442324633202711</v>
+        <v>0.04436349908148789</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.2797416374986396</v>
+        <v>0.2790438593190216</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.1655087139709394</v>
+        <v>0.165223517233056</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.1173491325193396</v>
+        <v>0.1171582131580835</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.08261457003914181</v>
+        <v>0.08248441954256415</v>
       </c>
       <c r="L63" s="181" t="n">
-        <v>0.04442324633202711</v>
+        <v>0.04436349908148789</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>5045.178010791935</v>
+        <v>5032.593487587962</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="Q63" s="184" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
       <c r="S63" s="51" t="inlineStr">
         <is>
@@ -6996,49 +6996,49 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.2705424474420638</v>
+        <v>0.2698676154142916</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.1596492164618506</v>
+        <v>0.1593741165311692</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.112938861428371</v>
+        <v>0.1127551172896459</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.07864285822027095</v>
+        <v>0.07851896473459638</v>
       </c>
       <c r="X63" s="187" t="n">
-        <v>0.04219224193455574</v>
+        <v>0.04213549528369566</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.2705424474420638</v>
+        <v>0.2698676154142916</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.1596492164618506</v>
+        <v>0.1593741165311692</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.112938861428371</v>
+        <v>0.1127551172896459</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.07864285822027095</v>
+        <v>0.07851896473459638</v>
       </c>
       <c r="AC63" s="187" t="n">
-        <v>0.04219224193455574</v>
+        <v>0.04213549528369566</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>5045.178010791935</v>
+        <v>5032.593487587962</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>3288.098638104912</v>
+        <v>3282.43274304158</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>2545.878556343138</v>
+        <v>2541.736578491427</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>1810.498234444591</v>
+        <v>1807.645986419161</v>
       </c>
       <c r="AH63" s="190" t="n">
-        <v>1070.97753995324</v>
+        <v>1069.537123759358</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" thickBot="1"/>
@@ -7297,46 +7297,46 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>2.43070826391962</v>
+        <v>2.430708263919618</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>2.983199484175708</v>
+        <v>2.983199484175707</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>3.407268361183442</v>
+        <v>3.407268361183443</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>1.691316923352675</v>
+        <v>1.691316923352677</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>1.718722771571375</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>2.43070826391962</v>
+        <v>2.430708263919618</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>2.983199484175708</v>
+        <v>2.983199484175707</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>3.407268361183442</v>
+        <v>3.407268361183443</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>1.691316923352675</v>
+        <v>1.691316923352677</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>1.718722771571375</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>33623.0254711829</v>
+        <v>33623.02547118288</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>45558.14129942619</v>
+        <v>45558.14129942618</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>56810.46337460833</v>
+        <v>56810.46337460835</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>28860.06500917254</v>
+        <v>28860.06500917259</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>32147.71167156056</v>
@@ -7347,46 +7347,46 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>2.424493550020262</v>
+        <v>2.42449355002026</v>
       </c>
       <c r="U68" s="149" t="n">
         <v>2.975572188224952</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>3.398556827036213</v>
+        <v>3.398556827036214</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>1.686992648429271</v>
+        <v>1.686992648429273</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>1.714328426739387</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>2.424493550020262</v>
+        <v>2.42449355002026</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>2.975572188224952</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>3.398556827036213</v>
+        <v>3.398556827036214</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>1.686992648429271</v>
+        <v>1.686992648429273</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>1.714328426739387</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>33623.0254711829</v>
+        <v>33623.02547118288</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>45558.14129942619</v>
+        <v>45558.14129942618</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>56810.46337460833</v>
+        <v>56810.46337460835</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>28860.06500917254</v>
+        <v>28860.06500917259</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>32147.71167156056</v>
@@ -7399,49 +7399,49 @@
         </is>
       </c>
       <c r="C69" s="155" t="n">
-        <v>10.49131164572394</v>
+        <v>10.34038053149144</v>
       </c>
       <c r="D69" s="156" t="n">
-        <v>13.68739032076246</v>
+        <v>13.5045281594945</v>
       </c>
       <c r="E69" s="156" t="n">
-        <v>16.46491189956748</v>
+        <v>16.25844190859365</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>3.838164368394891</v>
+        <v>3.791286230115063</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>4.142316816973359</v>
+        <v>4.098881663256663</v>
       </c>
       <c r="H69" s="155" t="n">
-        <v>10.49131164572394</v>
+        <v>10.34038053149144</v>
       </c>
       <c r="I69" s="156" t="n">
-        <v>13.68739032076246</v>
+        <v>13.5045281594945</v>
       </c>
       <c r="J69" s="156" t="n">
-        <v>16.46491189956748</v>
+        <v>16.25844190859365</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>3.838164368394891</v>
+        <v>3.791286230115063</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>4.142316816973359</v>
+        <v>4.098881663256663</v>
       </c>
       <c r="M69" s="158" t="n">
-        <v>29869.86551250784</v>
+        <v>29440.14878727689</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>41858.63309990075</v>
+        <v>41299.4059618568</v>
       </c>
       <c r="O69" s="159" t="n">
-        <v>54207.80349431779</v>
+        <v>53528.03765248072</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>11140.67922840668</v>
+        <v>11004.61045925732</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>13215.82741357803</v>
+        <v>13077.25001340189</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7449,49 +7449,49 @@
         </is>
       </c>
       <c r="T69" s="155" t="n">
-        <v>12.96817163689565</v>
+        <v>12.78160768180498</v>
       </c>
       <c r="U69" s="156" t="n">
-        <v>16.91880223700889</v>
+        <v>16.69276873678558</v>
       </c>
       <c r="V69" s="156" t="n">
-        <v>20.35205994352318</v>
+        <v>20.09684511708075</v>
       </c>
       <c r="W69" s="156" t="n">
-        <v>4.74430423771169</v>
+        <v>4.686358790682795</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>5.120263058700035</v>
+        <v>5.066573439375587</v>
       </c>
       <c r="Y69" s="155" t="n">
-        <v>12.96817163689565</v>
+        <v>12.78160768180498</v>
       </c>
       <c r="Z69" s="156" t="n">
-        <v>16.91880223700889</v>
+        <v>16.69276873678558</v>
       </c>
       <c r="AA69" s="156" t="n">
-        <v>20.35205994352318</v>
+        <v>20.09684511708075</v>
       </c>
       <c r="AB69" s="156" t="n">
-        <v>4.74430423771169</v>
+        <v>4.686358790682795</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>5.120263058700035</v>
+        <v>5.066573439375587</v>
       </c>
       <c r="AD69" s="158" t="n">
-        <v>29869.86551250784</v>
+        <v>29440.14878727689</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>41858.63309990075</v>
+        <v>41299.4059618568</v>
       </c>
       <c r="AF69" s="159" t="n">
-        <v>54207.80349431779</v>
+        <v>53528.03765248072</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>11140.67922840668</v>
+        <v>11004.61045925732</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>13215.82741357803</v>
+        <v>13077.25001340189</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>3.806594595722137</v>
+        <v>3.780831753006789</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>4.769117238440201</v>
+        <v>4.738607993474631</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>5.560466475913246</v>
+        <v>5.526419689905783</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>2.003415887166424</v>
+        <v>1.996600955618105</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>2.071880482789886</v>
+        <v>2.065551262967733</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>3.806594595722137</v>
+        <v>3.780831753006789</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>4.769117238440201</v>
+        <v>4.738607993474631</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>5.560466475913246</v>
+        <v>5.526419689905783</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>2.003415887166424</v>
+        <v>1.996600955618105</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>2.071880482789886</v>
+        <v>2.065551262967733</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>63492.89098369074</v>
+        <v>63063.17425845977</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>87416.77439932694</v>
+        <v>86857.54726128298</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>111018.2668689261</v>
+        <v>110338.5010270891</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>40000.74423757923</v>
+        <v>39864.67546842991</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>45363.53908513859</v>
+        <v>45224.96168496244</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,49 +7551,49 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>3.926249981525367</v>
+        <v>3.899677317115857</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>4.915250425898655</v>
+        <v>4.883806330102026</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>5.728626901946964</v>
+        <v>5.69355046814558</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>2.055998820865168</v>
+        <v>2.049005020268209</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>2.126404439162156</v>
+        <v>2.119908658523237</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>3.926249981525367</v>
+        <v>3.899677317115857</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>4.915250425898655</v>
+        <v>4.883806330102026</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>5.728626901946964</v>
+        <v>5.69355046814558</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>2.055998820865168</v>
+        <v>2.049005020268209</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>2.126404439162156</v>
+        <v>2.119908658523237</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>63492.89098369074</v>
+        <v>63063.17425845977</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>87416.77439932694</v>
+        <v>86857.54726128298</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>111018.2668689261</v>
+        <v>110338.5010270891</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>40000.74423757923</v>
+        <v>39864.67546842991</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>45363.53908513859</v>
+        <v>45224.96168496244</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,46 +7603,46 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>7.78699016401222</v>
+        <v>7.786990164012218</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>9.412648489771547</v>
+        <v>9.41264848977155</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>10.68676903652186</v>
       </c>
       <c r="F71" s="156" t="n">
-        <v>9.088546274422862</v>
+        <v>9.088546274422866</v>
       </c>
       <c r="G71" s="157" t="n">
         <v>9.656699521959776</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>7.78699016401222</v>
+        <v>7.786990164012218</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>9.412648489771547</v>
+        <v>9.41264848977155</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>10.68676903652186</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>9.088546274422862</v>
+        <v>9.088546274422866</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>9.656699521959776</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>616.945206175595</v>
+        <v>616.9452061755949</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>820.600006474925</v>
+        <v>820.6000064749253</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>1052.462049957358</v>
       </c>
       <c r="P71" s="159" t="n">
-        <v>985.9960064638117</v>
+        <v>985.996006463812</v>
       </c>
       <c r="Q71" s="160" t="n">
         <v>1201.602092032083</v>
@@ -7653,46 +7653,46 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>7.992117913661759</v>
+        <v>7.992117913661757</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>9.660599927012624</v>
+        <v>9.660599927012628</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>10.96828382430434</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>9.32796009228975</v>
+        <v>9.327960092289754</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>9.911079840961074</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>7.992117913661759</v>
+        <v>7.992117913661757</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>9.660599927012624</v>
+        <v>9.660599927012628</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>10.96828382430434</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>9.32796009228975</v>
+        <v>9.327960092289754</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>9.911079840961074</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>616.945206175595</v>
+        <v>616.9452061755949</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>820.600006474925</v>
+        <v>820.6000064749253</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>1052.462049957358</v>
       </c>
       <c r="AG71" s="159" t="n">
-        <v>985.9960064638117</v>
+        <v>985.996006463812</v>
       </c>
       <c r="AH71" s="160" t="n">
         <v>1201.602092032083</v>
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>3.825411870899384</v>
+        <v>3.799770821732541</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>4.791098396124026</v>
+        <v>4.760733573256232</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>5.585628414655156</v>
+        <v>5.551748743860606</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>2.041705259600715</v>
+        <v>2.034927157219666</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>2.114742615288161</v>
+        <v>2.108449162154339</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>3.825411870899384</v>
+        <v>3.799770821732541</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>4.791098396124026</v>
+        <v>4.760733573256232</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>5.585628414655156</v>
+        <v>5.551748743860606</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>2.041705259600715</v>
+        <v>2.034927157219666</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>2.114742615288161</v>
+        <v>2.108449162154339</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>64109.83618986634</v>
+        <v>63680.11946463537</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>88237.37440580186</v>
+        <v>87678.14726775791</v>
       </c>
       <c r="O72" s="165" t="n">
-        <v>112070.7289188835</v>
+        <v>111390.9630770464</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>40986.74024404304</v>
+        <v>40850.67147489372</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>46565.14117717067</v>
+        <v>46426.56377699452</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,49 +7755,49 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>3.945566224024512</v>
+        <v>3.919119801794568</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>4.937807209645031</v>
+        <v>4.906512581799883</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>5.754442469189541</v>
+        <v>5.719538855488565</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>2.095294216774431</v>
+        <v>2.088338208480417</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>2.170394851841117</v>
+        <v>2.163935778201042</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>3.945566224024512</v>
+        <v>3.919119801794568</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>4.937807209645031</v>
+        <v>4.906512581799883</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>5.754442469189541</v>
+        <v>5.719538855488565</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>2.095294216774431</v>
+        <v>2.088338208480417</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>2.170394851841117</v>
+        <v>2.163935778201042</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>64109.83618986634</v>
+        <v>63680.11946463537</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>88237.37440580186</v>
+        <v>87678.14726775791</v>
       </c>
       <c r="AF72" s="165" t="n">
-        <v>112070.7289188835</v>
+        <v>111390.9630770464</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>40986.74024404304</v>
+        <v>40850.67147489372</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>46565.14117717067</v>
+        <v>46426.56377699452</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7807,49 +7807,49 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>21.26220829018735</v>
+        <v>21.26207295196642</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>26.63876232705698</v>
+        <v>26.6386196656922</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>33.51838867357897</v>
+        <v>33.51823510568493</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>41.67366359428463</v>
+        <v>41.67350240975341</v>
       </c>
       <c r="G73" s="157" t="n">
-        <v>50.89769595749018</v>
+        <v>50.89753050847471</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>21.26220829018735</v>
+        <v>21.26207295196642</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>26.63876232705698</v>
+        <v>26.6386196656922</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>33.51838867357897</v>
+        <v>33.51823510568493</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>41.67366359428463</v>
+        <v>41.67350240975341</v>
       </c>
       <c r="L73" s="157" t="n">
-        <v>50.89769595749018</v>
+        <v>50.89753050847471</v>
       </c>
       <c r="M73" s="158" t="n">
-        <v>27134.77547668929</v>
+        <v>27134.6027584002</v>
       </c>
       <c r="N73" s="159" t="n">
-        <v>38617.6515691603</v>
+        <v>38617.44475599046</v>
       </c>
       <c r="O73" s="159" t="n">
-        <v>54661.3030800456</v>
+        <v>54661.05264374685</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>76689.56623833893</v>
+        <v>76689.26962002611</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>106335.3914081478</v>
+        <v>106335.0457523084</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7857,49 +7857,49 @@
         </is>
       </c>
       <c r="T73" s="155" t="n">
-        <v>11.30709026914539</v>
+        <v>11.30701829724764</v>
       </c>
       <c r="U73" s="156" t="n">
-        <v>14.16630324467998</v>
+        <v>14.16622737838673</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>17.82483932223384</v>
+        <v>17.82475765592634</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>22.16175618616435</v>
+        <v>22.16167046938368</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>27.06703061264136</v>
+        <v>27.06694262803847</v>
       </c>
       <c r="Y73" s="155" t="n">
-        <v>11.30709026914539</v>
+        <v>11.30701829724764</v>
       </c>
       <c r="Z73" s="156" t="n">
-        <v>14.16630324467998</v>
+        <v>14.16622737838673</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>17.82483932223384</v>
+        <v>17.82475765592634</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>22.16175618616435</v>
+        <v>22.16167046938368</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>27.06703061264136</v>
+        <v>27.06694262803847</v>
       </c>
       <c r="AD73" s="158" t="n">
-        <v>27134.77547668929</v>
+        <v>27134.6027584002</v>
       </c>
       <c r="AE73" s="159" t="n">
-        <v>38617.6515691603</v>
+        <v>38617.44475599046</v>
       </c>
       <c r="AF73" s="159" t="n">
-        <v>54661.3030800456</v>
+        <v>54661.05264374685</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>76689.56623833893</v>
+        <v>76689.26962002611</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>106335.3914081478</v>
+        <v>106335.0457523084</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7909,49 +7909,49 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>5.059269866381411</v>
+        <v>5.035433645614484</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>6.385335271440298</v>
+        <v>6.357175777456736</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>7.685307403808452</v>
+        <v>7.653962892052601</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>5.369669673728582</v>
+        <v>5.363447205438321</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>6.3421853119649</v>
+        <v>6.336422900608592</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>5.059269866381411</v>
+        <v>5.035433645614484</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>6.385335271440298</v>
+        <v>6.357175777456736</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>7.685307403808452</v>
+        <v>7.653962892052601</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>5.369669673728582</v>
+        <v>5.363447205438321</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>6.3421853119649</v>
+        <v>6.336422900608592</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>91244.61166655563</v>
+        <v>90814.72222303557</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>126855.0259749622</v>
+        <v>126295.5920237484</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>166732.0319989291</v>
+        <v>166052.0157207933</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>117676.306482382</v>
+        <v>117539.9410949198</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>152900.5325853184</v>
+        <v>152761.6095293029</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,49 +7959,49 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>4.892897833013387</v>
+        <v>4.869845456678866</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>6.159275535852775</v>
+        <v>6.132112971160094</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>7.396474513947616</v>
+        <v>7.366308006588469</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>5.111521740543481</v>
+        <v>5.105598418648817</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>6.023670919414283</v>
+        <v>6.01819790530238</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>4.892897833013387</v>
+        <v>4.869845456678866</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>6.159275535852775</v>
+        <v>6.132112971160094</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>7.396474513947616</v>
+        <v>7.366308006588469</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>5.111521740543481</v>
+        <v>5.105598418648817</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>6.023670919414283</v>
+        <v>6.01819790530238</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>91244.61166655563</v>
+        <v>90814.72222303557</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>126855.0259749622</v>
+        <v>126295.5920237484</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>166732.0319989291</v>
+        <v>166052.0157207933</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>117676.306482382</v>
+        <v>117539.9410949198</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>152900.5325853184</v>
+        <v>152761.6095293029</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8263,40 +8263,40 @@
         <v>440.9977874774131</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>482.420766217697</v>
+        <v>482.4207662176971</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>518.5831896033579</v>
+        <v>518.5831896033581</v>
       </c>
       <c r="F79" s="149" t="n">
         <v>589.0811871462283</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>624.58037419379</v>
+        <v>624.5803741937901</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>440.9977874774131</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>482.420766217697</v>
+        <v>482.4207662176971</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>518.5831896033579</v>
+        <v>518.5831896033581</v>
       </c>
       <c r="K79" s="149" t="n">
         <v>589.0811871462283</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>624.5803741937899</v>
+        <v>624.58037419379</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>6100147.870965851</v>
+        <v>6100147.87096585</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>7367322.751866227</v>
+        <v>7367322.751866229</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>8646501.589154691</v>
+        <v>8646501.589154692</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>10051883.90300027</v>
@@ -8313,40 +8313,40 @@
         <v>439.8702662852967</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>481.1873368153888</v>
+        <v>481.187336815389</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>517.2573019169417</v>
+        <v>517.2573019169419</v>
       </c>
       <c r="W79" s="149" t="n">
         <v>587.5750536887708</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>622.9834781818807</v>
+        <v>622.9834781818809</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>439.8702662852967</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>481.1873368153888</v>
+        <v>481.187336815389</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>517.2573019169417</v>
+        <v>517.2573019169419</v>
       </c>
       <c r="AB79" s="149" t="n">
         <v>587.5750536887708</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>622.9834781818807</v>
+        <v>622.9834781818809</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>6100147.870965851</v>
+        <v>6100147.87096585</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>7367322.751866227</v>
+        <v>7367322.751866229</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>8646501.589154691</v>
+        <v>8646501.589154692</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>10051883.90300027</v>
@@ -8362,49 +8362,49 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>847.2272929824632</v>
+        <v>858.8856315513456</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>948.4938925036162</v>
+        <v>959.8147013596573</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>1028.665222638489</v>
+        <v>1039.442714435912</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>1320.108854068171</v>
+        <v>1332.509602407463</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1407.301981120742</v>
+        <v>1418.147307190337</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>847.2272929824633</v>
+        <v>858.8856315513456</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>948.4938925036159</v>
+        <v>959.8147013596574</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>1028.665222638489</v>
+        <v>1039.442714435912</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1320.108854068171</v>
+        <v>1332.509602407463</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1407.301981120742</v>
+        <v>1418.147307190337</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>2412145.035289913</v>
+        <v>2445337.548953705</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>2900674.04475055</v>
+        <v>2935295.223309353</v>
       </c>
       <c r="O80" s="159" t="n">
-        <v>3386697.881553238</v>
+        <v>3422180.86263932</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>3831755.984932823</v>
+        <v>3867750.472448222</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>4489917.339269944</v>
+        <v>4524518.738417504</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,49 +8412,49 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>1047.24645705641</v>
+        <v>1061.657175245678</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1172.420762045276</v>
+        <v>1186.414264218426</v>
       </c>
       <c r="V80" s="156" t="n">
-        <v>1271.519483411637</v>
+        <v>1284.841398550931</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>1631.769103524745</v>
+        <v>1647.097504617036</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1739.547375237438</v>
+        <v>1752.953139423838</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>1047.24645705641</v>
+        <v>1061.657175245678</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>1172.420762045276</v>
+        <v>1186.414264218426</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>1271.519483411637</v>
+        <v>1284.841398550931</v>
       </c>
       <c r="AB80" s="156" t="n">
-        <v>1631.769103524745</v>
+        <v>1647.097504617036</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1739.547375237438</v>
+        <v>1752.953139423838</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>2412145.035289913</v>
+        <v>2445337.548953705</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>2900674.04475055</v>
+        <v>2935295.223309353</v>
       </c>
       <c r="AF80" s="159" t="n">
-        <v>3386697.881553238</v>
+        <v>3422180.86263932</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>3831755.984932823</v>
+        <v>3867750.472448222</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>4489917.339269944</v>
+        <v>4524518.738417504</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>510.338207508622</v>
+        <v>512.3282010523633</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>560.181737011917</v>
+        <v>562.0705330766822</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>602.6954314990891</v>
+        <v>604.4726338673046</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>695.3546803524655</v>
+        <v>697.1574450138044</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>738.6358496757613</v>
+        <v>740.2161929429942</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>510.338207508622</v>
+        <v>512.3282010523633</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>560.181737011917</v>
+        <v>562.0705330766822</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>602.6954314990891</v>
+        <v>604.4726338673046</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>695.3546803524655</v>
+        <v>697.1574450138044</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>738.6358496757613</v>
+        <v>740.2161929429942</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>8512292.906255763</v>
+        <v>8545485.419919554</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>10267996.79661678</v>
+        <v>10302617.97517558</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>12033199.47070793</v>
+        <v>12068682.45179401</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>13883639.88793309</v>
+        <v>13919634.37544849</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>16172330.65071977</v>
+        <v>16206932.04986733</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>526.3800300810066</v>
+        <v>528.4325765021912</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>577.3465787829988</v>
+        <v>579.2932505039081</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>620.9222333274046</v>
+        <v>622.7531821049693</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>713.6054036737221</v>
+        <v>715.4554848484564</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>758.0739153254196</v>
+        <v>759.6958471727233</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>526.3800300810066</v>
+        <v>528.4325765021912</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>577.3465787829988</v>
+        <v>579.2932505039081</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>620.9222333274046</v>
+        <v>622.7531821049693</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>713.6054036737221</v>
+        <v>715.4554848484564</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>758.0739153254196</v>
+        <v>759.6958471727233</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>8512292.906255763</v>
+        <v>8545485.419919554</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>10267996.79661678</v>
+        <v>10302617.97517558</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>12033199.47070793</v>
+        <v>12068682.45179401</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>13883639.88793309</v>
+        <v>13919634.37544849</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>16172330.65071977</v>
+        <v>16206932.04986733</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8572,7 +8572,7 @@
         <v>1295.745439939102</v>
       </c>
       <c r="E82" s="156" t="n">
-        <v>1387.669005945771</v>
+        <v>1387.669005945772</v>
       </c>
       <c r="F82" s="156" t="n">
         <v>1515.943949091569</v>
@@ -8602,13 +8602,13 @@
         <v>112963.8185851014</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>136661.4139099335</v>
+        <v>136661.4139099336</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>164461.3599023771</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>199565.0616840644</v>
+        <v>199565.0616840645</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8652,13 +8652,13 @@
         <v>112963.8185851014</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>136661.4139099335</v>
+        <v>136661.4139099336</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>164461.3599023771</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>199565.0616840644</v>
+        <v>199565.0616840645</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,49 +8668,49 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>513.4071708919009</v>
+        <v>515.387756763598</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>563.6636866027386</v>
+        <v>565.5435416435533</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>606.5483950650751</v>
+        <v>608.3168742148318</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>699.7892985470503</v>
+        <v>701.5823207303039</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>743.5249777154778</v>
+        <v>745.0963903962111</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>513.4071708919009</v>
+        <v>515.387756763598</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>563.6636866027386</v>
+        <v>565.5435416435533</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>606.5483950650751</v>
+        <v>608.3168742148318</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>699.7892985470503</v>
+        <v>701.5823207303039</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>743.5249777154778</v>
+        <v>745.0963903962111</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>8604158.384870606</v>
+        <v>8637350.898534399</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>10380960.61520188</v>
+        <v>10415581.79376068</v>
       </c>
       <c r="O83" s="165" t="n">
-        <v>12169860.88461786</v>
+        <v>12205343.86570395</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>14048101.24783547</v>
+        <v>14084095.73535087</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>16371895.71240383</v>
+        <v>16406497.11155139</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,49 +8718,49 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>529.5330440240442</v>
+        <v>531.5758391485626</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>580.9237017076804</v>
+        <v>582.8611200210117</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>624.8800645283724</v>
+        <v>626.7019922990304</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>718.1567776795657</v>
+        <v>719.996861596406</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>763.0918165561538</v>
+        <v>764.7045830307712</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>529.5330440240442</v>
+        <v>531.5758391485626</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>580.9237017076804</v>
+        <v>582.8611200210117</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>624.8800645283724</v>
+        <v>626.7019922990304</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>718.1567776795657</v>
+        <v>719.996861596406</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>763.0918165561538</v>
+        <v>764.7045830307712</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>8604158.384870606</v>
+        <v>8637350.898534399</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>10380960.61520188</v>
+        <v>10415581.79376068</v>
       </c>
       <c r="AF83" s="165" t="n">
-        <v>12169860.88461786</v>
+        <v>12205343.86570395</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>14048101.24783547</v>
+        <v>14084095.73535087</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>16371895.71240383</v>
+        <v>16406497.11155139</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>2448.482083137819</v>
+        <v>2448.510873316499</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>2579.547137570033</v>
+        <v>2579.571986500833</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>2716.740207236664</v>
+        <v>2716.762064282784</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>2873.239658420455</v>
+        <v>2873.258672577081</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3041.361145190371</v>
+        <v>3041.377595172966</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>2448.482083137819</v>
+        <v>2448.510873316499</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>2579.547137570032</v>
+        <v>2579.571986500833</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>2716.740207236664</v>
+        <v>2716.762064282784</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>2873.239658420455</v>
+        <v>2873.258672577081</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3041.361145190371</v>
+        <v>3041.377595172966</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>3124746.530458139</v>
+        <v>3124783.272410045</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>3739515.047353546</v>
+        <v>3739551.070324122</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>4430420.60594534</v>
+        <v>4430456.250099779</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>5287452.172390179</v>
+        <v>5287487.163012511</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>6354007.223774104</v>
+        <v>6354041.591053506</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>1302.08525655359</v>
+        <v>1302.100566964661</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>1371.784714924498</v>
+        <v>1371.797929408141</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>1444.743007960207</v>
+        <v>1444.754631380978</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>1527.968296578205</v>
+        <v>1527.97840817068</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>1617.374100582471</v>
+        <v>1617.38284856554</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>1302.08525655359</v>
+        <v>1302.100566964661</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>1371.784714924498</v>
+        <v>1371.797929408141</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>1444.743007960207</v>
+        <v>1444.754631380978</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>1527.968296578205</v>
+        <v>1527.97840817068</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>1617.374100582471</v>
+        <v>1617.38284856554</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>3124746.530458139</v>
+        <v>3124783.272410045</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>3739515.047353546</v>
+        <v>3739551.070324122</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>4430420.60594534</v>
+        <v>4430456.250099779</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>5287452.172390179</v>
+        <v>5287487.163012511</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>6354007.223774104</v>
+        <v>6354041.591053506</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,49 +8872,49 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>650.336432146005</v>
+        <v>652.1789055649631</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>710.7638866072633</v>
+        <v>712.5083807621791</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>765.1695041151374</v>
+        <v>766.8066913446187</v>
       </c>
       <c r="F85" s="180" t="n">
-        <v>882.2977023066999</v>
+        <v>883.9417579530708</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>942.6513130197382</v>
+        <v>944.0879754393353</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>650.336432146005</v>
+        <v>652.1789055649631</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>710.7638866072633</v>
+        <v>712.5083807621791</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>765.1695041151374</v>
+        <v>766.8066913446187</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>882.2977023066999</v>
+        <v>883.9417579530708</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>942.6513130197382</v>
+        <v>944.0879754393353</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>11728904.91532874</v>
+        <v>11762134.17094444</v>
       </c>
       <c r="N85" s="183" t="n">
-        <v>14120475.66255542</v>
+        <v>14155132.86408481</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>16600281.4905632</v>
+        <v>16635800.11580373</v>
       </c>
       <c r="P85" s="183" t="n">
-        <v>19335553.42022565</v>
+        <v>19371582.89836338</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>22725902.93617793</v>
+        <v>22760538.7026049</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,49 +8922,49 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>628.9503828845482</v>
+        <v>630.7322673139416</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>685.6007449018856</v>
+        <v>687.283478809198</v>
       </c>
       <c r="V85" s="186" t="n">
-        <v>736.4125387141909</v>
+        <v>737.9881963920367</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>839.8810655033628</v>
+        <v>841.446082848881</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>895.3099006224863</v>
+        <v>896.6744116249665</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>628.9503828845482</v>
+        <v>630.7322673139416</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>685.6007449018856</v>
+        <v>687.283478809198</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>736.4125387141909</v>
+        <v>737.9881963920367</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>839.8810655033628</v>
+        <v>841.446082848881</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>895.3099006224863</v>
+        <v>896.6744116249665</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>11728904.91532874</v>
+        <v>11762134.17094444</v>
       </c>
       <c r="AE85" s="189" t="n">
-        <v>14120475.66255542</v>
+        <v>14155132.86408481</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>16600281.4905632</v>
+        <v>16635800.11580373</v>
       </c>
       <c r="AG85" s="189" t="n">
-        <v>19335553.42022565</v>
+        <v>19371582.89836338</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>22725902.93617793</v>
+        <v>22760538.7026049</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
